--- a/sample-project2/srcs/Access/build/test-results/reports/report-normal.xlsx
+++ b/sample-project2/srcs/Access/build/test-results/reports/report-normal.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\開発\contextbase-evaluation\sample-project2\srcs\Access\.tmp\tests\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F06A513A-BD9C-41DD-ABFD-A7412DC98D59}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{6031258E-A458-44C4-B15D-A959D74967D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{01035AB0-D38B-48C5-AF39-47E1921B06F1}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{0B4FAB82-BDC6-4341-B980-BD3758D379B4}"/>
   </bookViews>
   <sheets>
     <sheet name="職務経歴書" sheetId="1" r:id="rId1"/>
@@ -54,7 +54,7 @@
     <t>2026年10月30日現在</t>
   </si>
   <si>
-    <t>作成日時（JST）：2026年10月30日 01:43</t>
+    <t>作成日時（JST）：2026年10月30日 11:34</t>
   </si>
   <si>
     <t>氏名</t>
@@ -781,7 +781,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2231F163-D2CB-4525-AFC6-8F8F5E7D16DA}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0CF9BD82-6982-4889-8379-22B3410468BB}">
   <dimension ref="A1:X15"/>
   <sheetFormatPr defaultRowHeight="18" customHeight="1"/>
   <cols>
@@ -1234,13 +1234,13 @@
   <pageSetup paperSize="9" fitToWidth="0" fitToHeight="0" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
   <headerFooter scaleWithDoc="0">
     <oddFooter>&amp;C&amp;11&amp;"メイリオ,Regular"山田 太郎
-職務経歴書 ／ 作成JST 2026年10月30日 01:43  &amp;P/&amp;N</oddFooter>
+職務経歴書 ／ 作成JST 2026年10月30日 11:34  &amp;P/&amp;N</oddFooter>
   </headerFooter>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FDA56759-6439-4A19-9A07-E9D82AFF68C4}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E785820B-74AD-4844-B3EA-595D481131AA}">
   <dimension ref="A1:X14"/>
   <sheetFormatPr defaultRowHeight="18" customHeight="1"/>
   <cols>
@@ -1692,7 +1692,7 @@
   <pageSetup paperSize="9" fitToWidth="0" fitToHeight="0" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
   <headerFooter scaleWithDoc="0">
     <oddFooter>&amp;C&amp;11&amp;"メイリオ,Regular"山田 太郎
-案件経歴 ／ 作成JST 2026年10月30日 01:43  &amp;P/&amp;N</oddFooter>
+案件経歴 ／ 作成JST 2026年10月30日 11:34  &amp;P/&amp;N</oddFooter>
   </headerFooter>
 </worksheet>
 </file>